--- a/Member.xlsx
+++ b/Member.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8131FEE-9E9C-4AD7-9F36-F003AE20803F}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{353A7F05-97C9-4AED-9496-137BA892B700}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -107,9 +107,6 @@
     <t>PaTTz</t>
   </si>
   <si>
-    <t>Alternaria</t>
-  </si>
-  <si>
     <t>Axion</t>
   </si>
   <si>
@@ -132,6 +129,9 @@
   </si>
   <si>
     <t>ヾOhZEッ</t>
+  </si>
+  <si>
+    <t>LLiamZayze</t>
   </si>
 </sst>
 </file>
@@ -184,10 +184,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -477,6 +473,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -491,13 +490,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2">
         <v>3307</v>
       </c>
       <c r="C2">
-        <f t="shared" ref="C2:C31" si="0">RANK(B2,$B$2:$B$31,0)</f>
+        <f>RANK(B2,$B$2:$B$31,0)</f>
         <v>1</v>
       </c>
     </row>
@@ -509,7 +508,7 @@
         <v>3178</v>
       </c>
       <c r="C3">
-        <f t="shared" si="0"/>
+        <f>RANK(B3,$B$2:$B$31,0)</f>
         <v>2</v>
       </c>
     </row>
@@ -521,7 +520,7 @@
         <v>3156</v>
       </c>
       <c r="C4">
-        <f t="shared" si="0"/>
+        <f>RANK(B4,$B$2:$B$31,0)</f>
         <v>3</v>
       </c>
     </row>
@@ -533,323 +532,326 @@
         <v>3123</v>
       </c>
       <c r="C5">
-        <f t="shared" si="0"/>
+        <f>RANK(B5,$B$2:$B$31,0)</f>
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="B6">
-        <v>3107</v>
+        <v>3122</v>
       </c>
       <c r="C6">
-        <f t="shared" si="0"/>
+        <f>RANK(B6,$B$2:$B$31,0)</f>
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7">
-        <v>3100</v>
+        <v>3107</v>
       </c>
       <c r="C7">
-        <f t="shared" si="0"/>
+        <f>RANK(B7,$B$2:$B$31,0)</f>
         <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8">
-        <v>3005</v>
+        <v>3100</v>
       </c>
       <c r="C8">
-        <f t="shared" si="0"/>
+        <f>RANK(B8,$B$2:$B$31,0)</f>
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B9">
-        <v>2928</v>
+        <v>3091</v>
       </c>
       <c r="C9">
-        <f t="shared" si="0"/>
+        <f>RANK(B9,$B$2:$B$31,0)</f>
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B10">
-        <v>2914</v>
+        <v>3005</v>
       </c>
       <c r="C10">
-        <f t="shared" si="0"/>
+        <f>RANK(B10,$B$2:$B$31,0)</f>
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B11">
-        <v>2874</v>
+        <v>2928</v>
       </c>
       <c r="C11">
-        <f t="shared" si="0"/>
+        <f>RANK(B11,$B$2:$B$31,0)</f>
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B12">
-        <v>2817</v>
+        <v>2914</v>
       </c>
       <c r="C12">
-        <f t="shared" si="0"/>
+        <f>RANK(B12,$B$2:$B$31,0)</f>
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B13">
-        <v>2800</v>
+        <v>2874</v>
       </c>
       <c r="C13">
-        <f t="shared" si="0"/>
+        <f>RANK(B13,$B$2:$B$31,0)</f>
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B14">
-        <v>2790</v>
+        <v>2817</v>
       </c>
       <c r="C14">
-        <f t="shared" si="0"/>
+        <f>RANK(B14,$B$2:$B$31,0)</f>
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B15">
-        <v>2747</v>
+        <v>2800</v>
       </c>
       <c r="C15">
-        <f t="shared" si="0"/>
+        <f>RANK(B15,$B$2:$B$31,0)</f>
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B16">
-        <v>2643</v>
+        <v>2790</v>
       </c>
       <c r="C16">
-        <f t="shared" si="0"/>
+        <f>RANK(B16,$B$2:$B$31,0)</f>
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B17">
-        <v>2578</v>
+        <v>2747</v>
       </c>
       <c r="C17">
-        <f t="shared" si="0"/>
+        <f>RANK(B17,$B$2:$B$31,0)</f>
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B18">
-        <v>2527</v>
+        <v>2643</v>
       </c>
       <c r="C18">
-        <f t="shared" si="0"/>
+        <f>RANK(B18,$B$2:$B$31,0)</f>
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B19">
-        <v>2526</v>
+        <v>2578</v>
       </c>
       <c r="C19">
-        <f t="shared" si="0"/>
+        <f>RANK(B19,$B$2:$B$31,0)</f>
         <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B20">
-        <v>2394</v>
+        <v>2527</v>
       </c>
       <c r="C20">
-        <f t="shared" si="0"/>
+        <f>RANK(B20,$B$2:$B$31,0)</f>
         <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B21">
-        <v>2241</v>
+        <v>2526</v>
       </c>
       <c r="C21">
-        <f t="shared" si="0"/>
+        <f>RANK(B21,$B$2:$B$31,0)</f>
         <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B22">
-        <v>1956</v>
+        <v>2394</v>
       </c>
       <c r="C22">
-        <f t="shared" si="0"/>
+        <f>RANK(B22,$B$2:$B$31,0)</f>
         <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B23">
-        <v>1924</v>
+        <v>2241</v>
       </c>
       <c r="C23">
-        <f t="shared" si="0"/>
+        <f>RANK(B23,$B$2:$B$31,0)</f>
         <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B24">
-        <v>1628</v>
+        <v>1956</v>
       </c>
       <c r="C24">
-        <f t="shared" si="0"/>
+        <f>RANK(B24,$B$2:$B$31,0)</f>
         <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B25">
-        <v>1182</v>
+        <v>1924</v>
       </c>
       <c r="C25">
-        <f t="shared" si="0"/>
+        <f>RANK(B25,$B$2:$B$31,0)</f>
         <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B26">
-        <v>1000</v>
+        <v>1182</v>
       </c>
       <c r="C26">
-        <f t="shared" si="0"/>
+        <f>RANK(B26,$B$2:$B$31,0)</f>
         <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B27">
         <v>1000</v>
       </c>
       <c r="C27">
-        <f t="shared" si="0"/>
-        <v>25</v>
+        <f>RANK(B27,$B$2:$B$31,0)</f>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C28">
-        <f t="shared" si="0"/>
-        <v>27</v>
+        <f>RANK(B28,$B$2:$B$31,0)</f>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <v>0</v>
       </c>
       <c r="C29">
-        <f t="shared" si="0"/>
-        <v>27</v>
+        <f>RANK(B29,$B$2:$B$31,0)</f>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
       <c r="C30">
-        <f t="shared" si="0"/>
-        <v>27</v>
+        <f>RANK(B30,$B$2:$B$31,0)</f>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31">
-        <f t="shared" si="0"/>
-        <v>27</v>
+        <f>RANK(B31,$B$2:$B$31,0)</f>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C31">
+    <sortCondition ref="C2:C31"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Member.xlsx
+++ b/Member.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{353A7F05-97C9-4AED-9496-137BA892B700}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5035ECB-36EB-470E-9ADF-2078140B72D9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,12 +38,6 @@
     <t>ID</t>
   </si>
   <si>
-    <t>RTA Score</t>
-  </si>
-  <si>
-    <t>Rank</t>
-  </si>
-  <si>
     <t>Bailu2</t>
   </si>
   <si>
@@ -132,6 +126,12 @@
   </si>
   <si>
     <t>LLiamZayze</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -474,383 +474,264 @@
   <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2">
-        <v>3307</v>
-      </c>
-      <c r="C2">
-        <f>RANK(B2,$B$2:$B$31,0)</f>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>3178</v>
-      </c>
-      <c r="C3">
-        <f>RANK(B3,$B$2:$B$31,0)</f>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
-        <v>3156</v>
-      </c>
-      <c r="C4">
-        <f>RANK(B4,$B$2:$B$31,0)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>3123</v>
-      </c>
-      <c r="C5">
-        <f>RANK(B5,$B$2:$B$31,0)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6">
-        <v>3122</v>
-      </c>
-      <c r="C6">
-        <f>RANK(B6,$B$2:$B$31,0)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>3107</v>
-      </c>
-      <c r="C7">
-        <f>RANK(B7,$B$2:$B$31,0)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>3100</v>
-      </c>
-      <c r="C8">
-        <f>RANK(B8,$B$2:$B$31,0)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9">
-        <v>3091</v>
-      </c>
-      <c r="C9">
-        <f>RANK(B9,$B$2:$B$31,0)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>3005</v>
-      </c>
-      <c r="C10">
-        <f>RANK(B10,$B$2:$B$31,0)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>2928</v>
-      </c>
-      <c r="C11">
-        <f>RANK(B11,$B$2:$B$31,0)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>2914</v>
-      </c>
-      <c r="C12">
-        <f>RANK(B12,$B$2:$B$31,0)</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13">
-        <v>2874</v>
-      </c>
-      <c r="C13">
-        <f>RANK(B13,$B$2:$B$31,0)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14">
-        <v>2817</v>
-      </c>
-      <c r="C14">
-        <f>RANK(B14,$B$2:$B$31,0)</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15">
-        <v>2800</v>
-      </c>
-      <c r="C15">
-        <f>RANK(B15,$B$2:$B$31,0)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16">
-        <v>2790</v>
-      </c>
-      <c r="C16">
-        <f>RANK(B16,$B$2:$B$31,0)</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17">
-        <v>2747</v>
-      </c>
-      <c r="C17">
-        <f>RANK(B17,$B$2:$B$31,0)</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18">
-        <v>2643</v>
-      </c>
-      <c r="C18">
-        <f>RANK(B18,$B$2:$B$31,0)</f>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19">
-        <v>2578</v>
-      </c>
-      <c r="C19">
-        <f>RANK(B19,$B$2:$B$31,0)</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20">
-        <v>2527</v>
-      </c>
-      <c r="C20">
-        <f>RANK(B20,$B$2:$B$31,0)</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21">
-        <v>2526</v>
-      </c>
-      <c r="C21">
-        <f>RANK(B21,$B$2:$B$31,0)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22">
-        <v>2394</v>
-      </c>
-      <c r="C22">
-        <f>RANK(B22,$B$2:$B$31,0)</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23">
-        <v>2241</v>
-      </c>
-      <c r="C23">
-        <f>RANK(B23,$B$2:$B$31,0)</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24">
-        <v>1956</v>
-      </c>
-      <c r="C24">
-        <f>RANK(B24,$B$2:$B$31,0)</f>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25">
-        <v>1924</v>
-      </c>
-      <c r="C25">
-        <f>RANK(B25,$B$2:$B$31,0)</f>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26">
-        <v>1182</v>
-      </c>
-      <c r="C26">
-        <f>RANK(B26,$B$2:$B$31,0)</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27">
-        <v>1000</v>
-      </c>
-      <c r="C27">
-        <f>RANK(B27,$B$2:$B$31,0)</f>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28">
-        <v>1000</v>
-      </c>
-      <c r="C28">
-        <f>RANK(B28,$B$2:$B$31,0)</f>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29">
-        <v>0</v>
-      </c>
-      <c r="C29">
-        <f>RANK(B29,$B$2:$B$31,0)</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30">
-        <v>0</v>
-      </c>
-      <c r="C30">
-        <f>RANK(B30,$B$2:$B$31,0)</f>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>30</v>
-      </c>
-      <c r="B31">
-        <v>0</v>
-      </c>
-      <c r="C31">
-        <f>RANK(B31,$B$2:$B$31,0)</f>
-        <v>28</v>
-      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C31">
-    <sortCondition ref="C2:C31"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D31">
+    <sortCondition ref="B2:B31"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Member.xlsx
+++ b/Member.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5035ECB-36EB-470E-9ADF-2078140B72D9}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{995E5B84-38D3-46A8-BCEC-92558A3D8177}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,6 +184,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -502,7 +506,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -510,7 +514,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -518,7 +522,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -526,7 +530,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -534,7 +538,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -542,7 +546,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -550,7 +554,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -558,7 +562,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -566,7 +570,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -574,7 +578,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -582,7 +586,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -590,7 +594,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -598,7 +602,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -606,7 +610,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -614,7 +618,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -622,7 +626,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -630,7 +634,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -638,7 +642,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -646,7 +650,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -654,7 +658,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -662,7 +666,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -670,7 +674,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
@@ -678,7 +682,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
@@ -686,7 +690,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
@@ -694,7 +698,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -702,7 +706,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
@@ -710,7 +714,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
@@ -718,7 +722,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
@@ -726,7 +730,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Member.xlsx
+++ b/Member.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{995E5B84-38D3-46A8-BCEC-92558A3D8177}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6992BE32-AC9C-4024-A522-242642CAA8DC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,12 +104,6 @@
     <t>Axion</t>
   </si>
   <si>
-    <t>Ely</t>
-  </si>
-  <si>
-    <t>Paul-Frost</t>
-  </si>
-  <si>
     <t>WCRz</t>
   </si>
   <si>
@@ -132,6 +126,12 @@
   </si>
   <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>Luminus</t>
+  </si>
+  <si>
+    <t>CloverZ</t>
   </si>
 </sst>
 </file>
@@ -484,13 +484,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -498,7 +498,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -538,7 +538,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -602,7 +602,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -610,7 +610,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -618,7 +618,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -626,7 +626,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -634,7 +634,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -642,7 +642,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -650,7 +650,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -658,7 +658,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -666,7 +666,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -674,7 +674,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
@@ -690,7 +690,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
@@ -722,7 +722,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
@@ -734,8 +734,8 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D31">
-    <sortCondition ref="B2:B31"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:B31">
+    <sortCondition ref="B5:B31"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Member.xlsx
+++ b/Member.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6992BE32-AC9C-4024-A522-242642CAA8DC}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="11_8947612F1371E0CEEB3B98154B88467870408069" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F8E1E26-7C93-4B4F-8AE3-8539D039EC26}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12552" yWindow="168" windowWidth="10488" windowHeight="12072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Members" sheetId="1" r:id="rId1"/>
@@ -80,15 +80,9 @@
     <t>Catzilla</t>
   </si>
   <si>
-    <t>Sora</t>
-  </si>
-  <si>
     <t>Mkay</t>
   </si>
   <si>
-    <t>Anohana</t>
-  </si>
-  <si>
     <t>Chai</t>
   </si>
   <si>
@@ -132,6 +126,12 @@
   </si>
   <si>
     <t>CloverZ</t>
+  </si>
+  <si>
+    <t>GMMFAFA</t>
+  </si>
+  <si>
+    <t>หอมหอย</t>
   </si>
 </sst>
 </file>
@@ -484,13 +484,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -498,7 +498,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -514,7 +514,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -522,7 +522,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -530,7 +530,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -538,7 +538,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -546,7 +546,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -554,7 +554,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -594,7 +594,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -602,7 +602,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -618,7 +618,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -626,7 +626,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -634,7 +634,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -642,7 +642,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -650,7 +650,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -658,7 +658,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -666,7 +666,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -674,7 +674,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
@@ -682,7 +682,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
@@ -690,7 +690,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
@@ -698,7 +698,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -706,7 +706,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
@@ -722,7 +722,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
@@ -734,8 +734,8 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:B31">
-    <sortCondition ref="B5:B31"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B10:B31">
+    <sortCondition ref="B31"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
